--- a/mainWidget/mainWidget/src/database/外防热材料.xlsx
+++ b/mainWidget/mainWidget/src/database/外防热材料.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VSProject\git\GFApp\mainWidget\mainWidget\src\database\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CC046BB-0832-4E2C-84F5-228A7C821BBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA2F00C8-BE03-4719-B230-F895D7D5AE9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13320" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="243" uniqueCount="130">
   <si>
     <r>
       <rPr>
@@ -407,10 +407,6 @@
     </r>
   </si>
   <si>
-    <t>2×10⁻⁶</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <r>
       <rPr>
         <sz val="12"/>
@@ -421,10 +417,6 @@
       </rPr>
       <t>碳化硼纤维增强陶瓷基复合材料</t>
     </r>
-  </si>
-  <si>
-    <t>1.5×10⁻⁶</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -697,6 +689,366 @@
       </rPr>
       <t>[GPa]</t>
     </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>13</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>20</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1500</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.35</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>40</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>60</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1300</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>6</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>15</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.0001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.0002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.003</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>30</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.0025</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.25</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>100</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>8</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>26</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>12</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>150</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.07</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.6</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>900</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>850</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1200</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.0003</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.0005</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.45</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>66</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.08</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1250</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1400</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1450</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1150</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>38</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>35</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.22</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>140</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>166</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>210</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>250</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>800</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>750</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.17</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>133</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>90</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>200</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1100</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>29</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.16</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>300</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>350</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>233</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.14</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>950</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>53</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>80</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.06</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.05</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1050</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.03</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1350</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.00002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.000015</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.00001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.000005</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.000003</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.00005</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.00004</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.000002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.0000015</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.00003</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.00006</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -704,10 +1056,6 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
-    <numFmt numFmtId="176" formatCode="0;[Red]0"/>
-    <numFmt numFmtId="177" formatCode="0.00_ "/>
-  </numFmts>
   <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -838,18 +1186,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -858,39 +1200,28 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="11" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="11" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="6" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="176" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="177" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="11" fontId="6" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1174,7 +1505,9 @@
   <dimension ref="A1:J31"/>
   <sheetFormatPr defaultRowHeight="14.15" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="5" max="5" width="17.640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.640625" style="12" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.640625" style="12" bestFit="1" customWidth="1"/>
+    <col min="6" max="10" width="9.140625" style="12"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="15.45" thickBot="1" x14ac:dyDescent="0.4">
@@ -1187,986 +1520,986 @@
       <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="17" t="s">
+      <c r="E1" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1" s="9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" ht="45.45" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A2" s="3">
+        <v>1</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" s="4">
+        <v>1200</v>
+      </c>
+      <c r="D2" s="10" t="s">
+        <v>119</v>
+      </c>
+      <c r="E2" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="F2" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="G2" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="H2" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="I2" s="10">
+        <v>0.3</v>
+      </c>
+      <c r="J2" s="10" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="45.45" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A3" s="5">
+        <v>2</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" s="6">
+        <v>1600</v>
+      </c>
+      <c r="D3" s="11" t="s">
+        <v>120</v>
+      </c>
+      <c r="E3" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="F3" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="G3" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="H3" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="I3" s="11">
+        <v>0.4</v>
+      </c>
+      <c r="J3" s="11" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="30.45" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A4" s="5">
+        <v>3</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" s="6">
+        <v>1700</v>
+      </c>
+      <c r="D4" s="11" t="s">
+        <v>121</v>
+      </c>
+      <c r="E4" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="F4" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="G4" s="10" t="s">
+        <v>111</v>
+      </c>
+      <c r="H4" s="11" t="s">
+        <v>112</v>
+      </c>
+      <c r="I4" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="J4" s="11" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="16.3" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A5" s="5">
         <v>4</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="B5" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" s="6">
+        <v>1800</v>
+      </c>
+      <c r="D5" s="11" t="s">
+        <v>122</v>
+      </c>
+      <c r="E5" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="F5" s="11" t="s">
+        <v>88</v>
+      </c>
+      <c r="G5" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="H5" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="I5" s="11" t="s">
+        <v>106</v>
+      </c>
+      <c r="J5" s="11" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="46.3" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="5">
         <v>5</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="B6" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C6" s="6">
+        <v>2000</v>
+      </c>
+      <c r="D6" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="E6" s="11">
+        <v>25</v>
+      </c>
+      <c r="F6" s="11" t="s">
+        <v>95</v>
+      </c>
+      <c r="G6" s="10" t="s">
+        <v>96</v>
+      </c>
+      <c r="H6" s="11" t="s">
+        <v>98</v>
+      </c>
+      <c r="I6" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="J6" s="11" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" ht="30.45" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A7" s="5">
         <v>6</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="B7" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C7" s="6">
+        <v>20</v>
+      </c>
+      <c r="D7" s="11" t="s">
+        <v>124</v>
+      </c>
+      <c r="E7" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="F7" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="G7" s="10" t="s">
+        <v>113</v>
+      </c>
+      <c r="H7" s="11" t="s">
+        <v>100</v>
+      </c>
+      <c r="I7" s="11" t="s">
+        <v>115</v>
+      </c>
+      <c r="J7" s="11" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="30.45" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A8" s="5">
         <v>7</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="B8" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C8" s="6">
+        <v>30</v>
+      </c>
+      <c r="D8" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="E8" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="F8" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="G8" s="10" t="s">
+        <v>113</v>
+      </c>
+      <c r="H8" s="11" t="s">
+        <v>99</v>
+      </c>
+      <c r="I8" s="11" t="s">
+        <v>114</v>
+      </c>
+      <c r="J8" s="11" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="30.45" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A9" s="5">
         <v>8</v>
       </c>
-    </row>
-    <row r="2" spans="1:10" ht="45.45" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="5">
-        <v>1</v>
-      </c>
-      <c r="B2" s="6" t="s">
+      <c r="B9" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C9" s="6">
+        <v>100</v>
+      </c>
+      <c r="D9" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="E9" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="F9" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="G9" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="H9" s="11" t="s">
+        <v>106</v>
+      </c>
+      <c r="I9" s="11" t="s">
+        <v>115</v>
+      </c>
+      <c r="J9" s="11" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" ht="30.45" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A10" s="5">
         <v>9</v>
       </c>
-      <c r="C2" s="6">
-        <v>1200</v>
-      </c>
-      <c r="D2" s="7">
-        <v>2.0000000000000002E-5</v>
-      </c>
-      <c r="E2" s="15">
-        <v>2</v>
-      </c>
-      <c r="F2" s="6">
-        <v>0.35</v>
-      </c>
-      <c r="G2" s="6">
+      <c r="B10" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C10" s="6">
+        <v>300</v>
+      </c>
+      <c r="D10" s="11" t="s">
+        <v>121</v>
+      </c>
+      <c r="E10" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="F10" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="G10" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="H10" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="I10" s="11" t="s">
+        <v>117</v>
+      </c>
+      <c r="J10" s="11" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="30.45" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A11" s="5">
+        <v>10</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C11" s="6">
+        <v>200</v>
+      </c>
+      <c r="D11" s="11" t="s">
+        <v>119</v>
+      </c>
+      <c r="E11" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="F11" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="G11" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="H11" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="I11" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="J11" s="11" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" ht="45.45" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A12" s="5">
+        <v>11</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="C12" s="6">
+        <v>300</v>
+      </c>
+      <c r="D12" s="11" t="s">
+        <v>120</v>
+      </c>
+      <c r="E12" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="F12" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="G12" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="H12" s="11" t="s">
+        <v>78</v>
+      </c>
+      <c r="I12" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="J12" s="11" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" ht="45.45" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A13" s="5">
+        <v>12</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C13" s="6">
+        <v>400</v>
+      </c>
+      <c r="D13" s="11" t="s">
+        <v>121</v>
+      </c>
+      <c r="E13" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="F13" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="G13" s="10" t="s">
+        <v>89</v>
+      </c>
+      <c r="H13" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="I13" s="11" t="s">
+        <v>114</v>
+      </c>
+      <c r="J13" s="11" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" ht="60.45" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A14" s="5">
         <v>13</v>
       </c>
-      <c r="H2" s="8">
+      <c r="B14" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="C14" s="6">
+        <v>2500</v>
+      </c>
+      <c r="D14" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="E14" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="F14" s="11" t="s">
+        <v>88</v>
+      </c>
+      <c r="G14" s="10" t="s">
+        <v>89</v>
+      </c>
+      <c r="H14" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="I14" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="J14" s="11" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" ht="60.45" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A15" s="5">
+        <v>14</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C15" s="6">
+        <v>2800</v>
+      </c>
+      <c r="D15" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="E15" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="F15" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="G15" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="H15" s="11" t="s">
+        <v>92</v>
+      </c>
+      <c r="I15" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="J15" s="11" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" ht="45.45" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A16" s="5">
+        <v>15</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C16" s="6">
+        <v>1800</v>
+      </c>
+      <c r="D16" s="11" t="s">
+        <v>119</v>
+      </c>
+      <c r="E16" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="F16" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="G16" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="H16" s="11" t="s">
+        <v>97</v>
+      </c>
+      <c r="I16" s="11" t="s">
+        <v>100</v>
+      </c>
+      <c r="J16" s="11" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" ht="45.45" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A17" s="5">
+        <v>16</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C17" s="6">
+        <v>1400</v>
+      </c>
+      <c r="D17" s="11" t="s">
+        <v>121</v>
+      </c>
+      <c r="E17" s="11" t="s">
+        <v>78</v>
+      </c>
+      <c r="F17" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="G17" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="H17" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="I17" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="J17" s="11" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" ht="61.3" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A18" s="5">
+        <v>17</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C18" s="6">
+        <v>1750</v>
+      </c>
+      <c r="D18" s="11" t="s">
+        <v>122</v>
+      </c>
+      <c r="E18" s="11">
+        <v>24</v>
+      </c>
+      <c r="F18" s="11" t="s">
+        <v>95</v>
+      </c>
+      <c r="G18" s="10" t="s">
+        <v>96</v>
+      </c>
+      <c r="H18" s="11" t="s">
+        <v>98</v>
+      </c>
+      <c r="I18" s="11" t="s">
+        <v>99</v>
+      </c>
+      <c r="J18" s="11" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" ht="61.3" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A19" s="5">
+        <v>18</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="C19" s="6">
+        <v>1900</v>
+      </c>
+      <c r="D19" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="E19" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="F19" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="G19" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="H19" s="11" t="s">
+        <v>104</v>
+      </c>
+      <c r="I19" s="11" t="s">
+        <v>105</v>
+      </c>
+      <c r="J19" s="11" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" ht="61.3" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A20" s="5">
+        <v>19</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="C20" s="6">
+        <v>2000</v>
+      </c>
+      <c r="D20" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="E20" s="11" t="s">
+        <v>86</v>
+      </c>
+      <c r="F20" s="11" t="s">
+        <v>109</v>
+      </c>
+      <c r="G20" s="10" t="s">
+        <v>108</v>
+      </c>
+      <c r="H20" s="11" t="s">
+        <v>107</v>
+      </c>
+      <c r="I20" s="11" t="s">
+        <v>106</v>
+      </c>
+      <c r="J20" s="11" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" ht="45.45" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A21" s="5">
         <v>20</v>
       </c>
-      <c r="I2" s="9">
-        <v>0.3</v>
-      </c>
-      <c r="J2" s="6">
-        <v>1500</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" ht="45.45" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="10">
-        <v>2</v>
-      </c>
-      <c r="B3" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3" s="11">
-        <v>1600</v>
-      </c>
-      <c r="D3" s="12">
-        <v>1.5E-5</v>
-      </c>
-      <c r="E3" s="16">
-        <v>4</v>
-      </c>
-      <c r="F3" s="11">
-        <v>0.3</v>
-      </c>
-      <c r="G3" s="6">
-        <v>40</v>
-      </c>
-      <c r="H3" s="13">
-        <v>60</v>
-      </c>
-      <c r="I3" s="14">
-        <v>0.4</v>
-      </c>
-      <c r="J3" s="11">
-        <v>1300</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" ht="30.45" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="10">
-        <v>3</v>
-      </c>
-      <c r="B4" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="C4" s="11">
-        <v>1700</v>
-      </c>
-      <c r="D4" s="12">
-        <v>1.0000000000000001E-5</v>
-      </c>
-      <c r="E4" s="16">
-        <v>6</v>
-      </c>
-      <c r="F4" s="11">
-        <v>0.25</v>
-      </c>
-      <c r="G4" s="6">
-        <v>53</v>
-      </c>
-      <c r="H4" s="13">
-        <v>80</v>
-      </c>
-      <c r="I4" s="14">
-        <v>0.35</v>
-      </c>
-      <c r="J4" s="11">
-        <v>1200</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" ht="16.3" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="10">
-        <v>4</v>
-      </c>
-      <c r="B5" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="C5" s="11">
-        <v>1800</v>
-      </c>
-      <c r="D5" s="12">
-        <v>5.0000000000000004E-6</v>
-      </c>
-      <c r="E5" s="16">
-        <v>15</v>
-      </c>
-      <c r="F5" s="11">
-        <v>0.22</v>
-      </c>
-      <c r="G5" s="6">
-        <v>100</v>
-      </c>
-      <c r="H5" s="13">
-        <v>150</v>
-      </c>
-      <c r="I5" s="14">
-        <v>1.5</v>
-      </c>
-      <c r="J5" s="11">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" ht="46.3" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="10">
-        <v>5</v>
-      </c>
-      <c r="B6" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="C6" s="11">
-        <v>2000</v>
-      </c>
-      <c r="D6" s="12">
-        <v>3.0000000000000001E-6</v>
-      </c>
-      <c r="E6" s="16">
-        <v>25</v>
-      </c>
-      <c r="F6" s="11">
-        <v>0.17</v>
-      </c>
-      <c r="G6" s="6">
-        <v>133</v>
-      </c>
-      <c r="H6" s="13">
-        <v>200</v>
-      </c>
-      <c r="I6" s="14">
-        <v>2</v>
-      </c>
-      <c r="J6" s="11">
-        <v>900</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" ht="30.45" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="10">
-        <v>6</v>
-      </c>
-      <c r="B7" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="C7" s="11">
-        <v>20</v>
-      </c>
-      <c r="D7" s="12">
-        <v>5.0000000000000002E-5</v>
-      </c>
-      <c r="E7" s="16">
-        <v>1E-4</v>
-      </c>
-      <c r="F7" s="11">
-        <v>0.35</v>
-      </c>
-      <c r="G7" s="6">
-        <v>0</v>
-      </c>
-      <c r="H7" s="13">
-        <v>0.5</v>
-      </c>
-      <c r="I7" s="14">
-        <v>0.05</v>
-      </c>
-      <c r="J7" s="11">
-        <v>1300</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" ht="30.45" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A8" s="10">
-        <v>7</v>
-      </c>
-      <c r="B8" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="C8" s="11">
-        <v>30</v>
-      </c>
-      <c r="D8" s="12">
-        <v>6.0000000000000002E-5</v>
-      </c>
-      <c r="E8" s="16">
-        <v>1E-4</v>
-      </c>
-      <c r="F8" s="11">
-        <v>0.35</v>
-      </c>
-      <c r="G8" s="6">
-        <v>0</v>
-      </c>
-      <c r="H8" s="13">
-        <v>1</v>
-      </c>
-      <c r="I8" s="14">
-        <v>0.06</v>
-      </c>
-      <c r="J8" s="11">
-        <v>1400</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" ht="30.45" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A9" s="10">
-        <v>8</v>
-      </c>
-      <c r="B9" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="C9" s="11">
-        <v>100</v>
-      </c>
-      <c r="D9" s="12">
-        <v>4.0000000000000003E-5</v>
-      </c>
-      <c r="E9" s="16">
-        <v>2.0000000000000001E-4</v>
-      </c>
-      <c r="F9" s="11">
-        <v>0.35</v>
-      </c>
-      <c r="G9" s="6">
-        <v>1</v>
-      </c>
-      <c r="H9" s="13">
-        <v>1.5</v>
-      </c>
-      <c r="I9" s="14">
-        <v>0.05</v>
-      </c>
-      <c r="J9" s="11">
-        <v>1350</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" ht="30.45" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A10" s="10">
-        <v>9</v>
-      </c>
-      <c r="B10" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="C10" s="11">
-        <v>300</v>
-      </c>
-      <c r="D10" s="12">
-        <v>1.0000000000000001E-5</v>
-      </c>
-      <c r="E10" s="16">
-        <v>1E-3</v>
-      </c>
-      <c r="F10" s="11">
-        <v>0.35</v>
-      </c>
-      <c r="G10" s="6">
-        <v>3</v>
-      </c>
-      <c r="H10" s="13">
-        <v>5</v>
-      </c>
-      <c r="I10" s="14">
-        <v>0.03</v>
-      </c>
-      <c r="J10" s="11">
-        <v>1100</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" ht="30.45" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="10">
-        <v>10</v>
-      </c>
-      <c r="B11" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="C11" s="11">
-        <v>200</v>
-      </c>
-      <c r="D11" s="12">
-        <v>2.0000000000000002E-5</v>
-      </c>
-      <c r="E11" s="16">
-        <v>1E-3</v>
-      </c>
-      <c r="F11" s="11">
-        <v>0.35</v>
-      </c>
-      <c r="G11" s="6">
-        <v>5</v>
-      </c>
-      <c r="H11" s="13">
-        <v>8</v>
-      </c>
-      <c r="I11" s="14">
-        <v>0.08</v>
-      </c>
-      <c r="J11" s="11">
-        <v>1050</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" ht="45.45" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="10">
-        <v>11</v>
-      </c>
-      <c r="B12" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="C12" s="11">
-        <v>300</v>
-      </c>
-      <c r="D12" s="12">
-        <v>1.5E-5</v>
-      </c>
-      <c r="E12" s="16">
-        <v>2E-3</v>
-      </c>
-      <c r="F12" s="11">
-        <v>0.35</v>
-      </c>
-      <c r="G12" s="6">
-        <v>6</v>
-      </c>
-      <c r="H12" s="13">
-        <v>10</v>
-      </c>
-      <c r="I12" s="14">
-        <v>7.0000000000000007E-2</v>
-      </c>
-      <c r="J12" s="11">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" ht="45.45" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="10">
-        <v>12</v>
-      </c>
-      <c r="B13" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="C13" s="11">
-        <v>400</v>
-      </c>
-      <c r="D13" s="12">
-        <v>1.0000000000000001E-5</v>
-      </c>
-      <c r="E13" s="16">
-        <v>3.0000000000000001E-3</v>
-      </c>
-      <c r="F13" s="11">
-        <v>0.35</v>
-      </c>
-      <c r="G13" s="6">
-        <v>140</v>
-      </c>
-      <c r="H13" s="13">
-        <v>210</v>
-      </c>
-      <c r="I13" s="14">
-        <v>0.06</v>
-      </c>
-      <c r="J13" s="11">
-        <v>950</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" ht="60.45" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="10">
-        <v>13</v>
-      </c>
-      <c r="B14" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="C14" s="11">
-        <v>2500</v>
-      </c>
-      <c r="D14" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="E14" s="16">
-        <v>30</v>
-      </c>
-      <c r="F14" s="11">
-        <v>0.22</v>
-      </c>
-      <c r="G14" s="6">
-        <v>140</v>
-      </c>
-      <c r="H14" s="13">
-        <v>210</v>
-      </c>
-      <c r="I14" s="14">
-        <v>5</v>
-      </c>
-      <c r="J14" s="11">
-        <v>800</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" ht="60.45" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="10">
-        <v>14</v>
-      </c>
-      <c r="B15" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="C15" s="11">
-        <v>2800</v>
-      </c>
-      <c r="D15" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="E15" s="16">
-        <v>35</v>
-      </c>
-      <c r="F15" s="11">
-        <v>0.2</v>
-      </c>
-      <c r="G15" s="6">
-        <v>166</v>
-      </c>
-      <c r="H15" s="13">
-        <v>250</v>
-      </c>
-      <c r="I15" s="14">
-        <v>4</v>
-      </c>
-      <c r="J15" s="11">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" ht="45.45" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A16" s="10">
-        <v>15</v>
-      </c>
-      <c r="B16" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="C16" s="11">
-        <v>1800</v>
-      </c>
-      <c r="D16" s="12">
-        <v>2.0000000000000002E-5</v>
-      </c>
-      <c r="E16" s="16">
-        <v>6</v>
-      </c>
-      <c r="F16" s="11">
-        <v>0.3</v>
-      </c>
-      <c r="G16" s="6">
-        <v>60</v>
-      </c>
-      <c r="H16" s="13">
-        <v>90</v>
-      </c>
-      <c r="I16" s="14">
-        <v>0.5</v>
-      </c>
-      <c r="J16" s="11">
-        <v>1300</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" ht="45.45" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="10">
-        <v>16</v>
-      </c>
-      <c r="B17" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="C17" s="11">
-        <v>1400</v>
-      </c>
-      <c r="D17" s="12">
-        <v>1.0000000000000001E-5</v>
-      </c>
-      <c r="E17" s="16">
-        <v>10</v>
-      </c>
-      <c r="F17" s="11">
-        <v>0.25</v>
-      </c>
-      <c r="G17" s="6">
-        <v>100</v>
-      </c>
-      <c r="H17" s="13">
-        <v>150</v>
-      </c>
-      <c r="I17" s="14">
-        <v>0.3</v>
-      </c>
-      <c r="J17" s="11">
-        <v>1400</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" ht="61.3" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A18" s="10">
-        <v>17</v>
-      </c>
-      <c r="B18" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="C18" s="11">
-        <v>1750</v>
-      </c>
-      <c r="D18" s="12">
-        <v>5.0000000000000004E-6</v>
-      </c>
-      <c r="E18" s="16">
-        <v>24</v>
-      </c>
-      <c r="F18" s="11">
-        <v>0.17</v>
-      </c>
-      <c r="G18" s="6">
-        <v>133</v>
-      </c>
-      <c r="H18" s="13">
-        <v>200</v>
-      </c>
-      <c r="I18" s="14">
-        <v>1</v>
-      </c>
-      <c r="J18" s="11">
-        <v>1100</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" ht="61.3" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A19" s="10">
-        <v>18</v>
-      </c>
-      <c r="B19" s="11" t="s">
+      <c r="B21" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="C19" s="11">
-        <v>1900</v>
-      </c>
-      <c r="D19" s="12">
-        <v>3.0000000000000001E-6</v>
-      </c>
-      <c r="E19" s="16">
-        <v>29</v>
-      </c>
-      <c r="F19" s="11">
-        <v>0.16</v>
-      </c>
-      <c r="G19" s="6">
-        <v>200</v>
-      </c>
-      <c r="H19" s="13">
-        <v>300</v>
-      </c>
-      <c r="I19" s="14">
-        <v>1.2</v>
-      </c>
-      <c r="J19" s="11">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10" ht="61.3" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A20" s="10">
-        <v>19</v>
-      </c>
-      <c r="B20" s="11" t="s">
-        <v>29</v>
-      </c>
-      <c r="C20" s="11">
-        <v>2000</v>
-      </c>
-      <c r="D20" s="12">
-        <v>1.9999999999999999E-6</v>
-      </c>
-      <c r="E20" s="16">
-        <v>38</v>
-      </c>
-      <c r="F20" s="11">
-        <v>0.14000000000000001</v>
-      </c>
-      <c r="G20" s="6">
-        <v>233</v>
-      </c>
-      <c r="H20" s="13">
-        <v>350</v>
-      </c>
-      <c r="I20" s="14">
-        <v>1.5</v>
-      </c>
-      <c r="J20" s="11">
-        <v>950</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" ht="45.45" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A21" s="10">
-        <v>20</v>
-      </c>
-      <c r="B21" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="C21" s="11">
+      <c r="C21" s="6">
         <v>2200</v>
       </c>
-      <c r="D21" s="12">
-        <v>3.0000000000000001E-6</v>
-      </c>
-      <c r="E21" s="16">
-        <v>30</v>
+      <c r="D21" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="E21" s="11" t="s">
+        <v>57</v>
       </c>
       <c r="F21" s="11">
         <v>0.15</v>
       </c>
-      <c r="G21" s="6">
-        <v>200</v>
-      </c>
-      <c r="H21" s="13">
-        <v>300</v>
-      </c>
-      <c r="I21" s="14">
+      <c r="G21" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="H21" s="11" t="s">
+        <v>104</v>
+      </c>
+      <c r="I21" s="11">
         <v>1.3</v>
       </c>
-      <c r="J21" s="11">
-        <v>900</v>
+      <c r="J21" s="11" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="22" spans="1:10" ht="45.45" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A22" s="10">
+      <c r="A22" s="5">
         <v>21</v>
       </c>
-      <c r="B22" s="11" t="s">
+      <c r="B22" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C22" s="6">
+        <v>1900</v>
+      </c>
+      <c r="D22" s="11" t="s">
+        <v>121</v>
+      </c>
+      <c r="E22" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="F22" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="G22" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="H22" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="I22" s="11" t="s">
+        <v>81</v>
+      </c>
+      <c r="J22" s="11" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" ht="30.45" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A23" s="5">
+        <v>22</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C23" s="6">
+        <v>1300</v>
+      </c>
+      <c r="D23" s="11" t="s">
+        <v>119</v>
+      </c>
+      <c r="E23" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="F23" s="11" t="s">
+        <v>76</v>
+      </c>
+      <c r="G23" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="H23" s="11">
+        <v>5</v>
+      </c>
+      <c r="I23" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="J23" s="11" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" ht="30.45" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A24" s="5">
+        <v>23</v>
+      </c>
+      <c r="B24" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="C22" s="11">
-        <v>1900</v>
-      </c>
-      <c r="D22" s="12">
-        <v>1.0000000000000001E-5</v>
-      </c>
-      <c r="E22" s="16">
-        <v>6</v>
-      </c>
-      <c r="F22" s="11">
-        <v>0.25</v>
-      </c>
-      <c r="G22" s="6">
+      <c r="C24" s="6">
+        <v>1500</v>
+      </c>
+      <c r="D24" s="11" t="s">
+        <v>120</v>
+      </c>
+      <c r="E24" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="F24" s="11" t="s">
+        <v>76</v>
+      </c>
+      <c r="G24" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="H24" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="I24" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="J24" s="11" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" ht="45.45" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A25" s="5">
+        <v>24</v>
+      </c>
+      <c r="B25" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="C25" s="6">
+        <v>1200</v>
+      </c>
+      <c r="D25" s="11" t="s">
+        <v>119</v>
+      </c>
+      <c r="E25" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="F25" s="11" t="s">
+        <v>76</v>
+      </c>
+      <c r="G25" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="H25" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="I25" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="J25" s="11" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" ht="30.45" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A26" s="5">
+        <v>25</v>
+      </c>
+      <c r="B26" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="C26" s="6">
+        <v>1000</v>
+      </c>
+      <c r="D26" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="E26" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="F26" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="G26" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="H26" s="11" t="s">
+        <v>78</v>
+      </c>
+      <c r="I26" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="J26" s="11" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" ht="30.45" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A27" s="5">
+        <v>26</v>
+      </c>
+      <c r="B27" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="C27" s="6">
+        <v>600</v>
+      </c>
+      <c r="D27" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="E27" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="F27" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="G27" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="H27" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="I27" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="J27" s="11" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" ht="30.45" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A28" s="5">
+        <v>27</v>
+      </c>
+      <c r="B28" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="C28" s="6">
+        <v>2900</v>
+      </c>
+      <c r="D28" s="11" t="s">
+        <v>121</v>
+      </c>
+      <c r="E28" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="F28" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="G28" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="H28" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="I28" s="11" t="s">
+        <v>69</v>
+      </c>
+      <c r="J28" s="11" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" ht="45.45" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A29" s="5">
+        <v>28</v>
+      </c>
+      <c r="B29" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="C29" s="6">
+        <v>400</v>
+      </c>
+      <c r="D29" s="11" t="s">
+        <v>120</v>
+      </c>
+      <c r="E29" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="F29" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="G29" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="H29" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="I29" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="J29" s="11" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" ht="45.45" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A30" s="5">
+        <v>29</v>
+      </c>
+      <c r="B30" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="C30" s="6">
+        <v>2200</v>
+      </c>
+      <c r="D30" s="11" t="s">
+        <v>121</v>
+      </c>
+      <c r="E30" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="F30" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="G30" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="H30" s="11" t="s">
         <v>66</v>
       </c>
-      <c r="H22" s="13">
-        <v>100</v>
-      </c>
-      <c r="I22" s="14">
-        <v>0.4</v>
-      </c>
-      <c r="J22" s="11">
-        <v>1250</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10" ht="30.45" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A23" s="10">
-        <v>22</v>
-      </c>
-      <c r="B23" s="11" t="s">
-        <v>32</v>
-      </c>
-      <c r="C23" s="11">
-        <v>1300</v>
-      </c>
-      <c r="D23" s="12">
-        <v>2.0000000000000002E-5</v>
-      </c>
-      <c r="E23" s="16">
-        <v>1E-4</v>
-      </c>
-      <c r="F23" s="11">
-        <v>0.45</v>
-      </c>
-      <c r="G23" s="6">
-        <v>3</v>
-      </c>
-      <c r="H23" s="13">
-        <v>5</v>
-      </c>
-      <c r="I23" s="14">
-        <v>0.3</v>
-      </c>
-      <c r="J23" s="11">
-        <v>1400</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10" ht="30.45" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A24" s="10">
-        <v>23</v>
-      </c>
-      <c r="B24" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="C24" s="11">
-        <v>1500</v>
-      </c>
-      <c r="D24" s="12">
-        <v>1.5E-5</v>
-      </c>
-      <c r="E24" s="16">
-        <v>2.0000000000000001E-4</v>
-      </c>
-      <c r="F24" s="11">
-        <v>0.45</v>
-      </c>
-      <c r="G24" s="6">
-        <v>5</v>
-      </c>
-      <c r="H24" s="13">
-        <v>8</v>
-      </c>
-      <c r="I24" s="14">
-        <v>0.35</v>
-      </c>
-      <c r="J24" s="11">
-        <v>1300</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10" ht="45.45" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A25" s="10">
-        <v>24</v>
-      </c>
-      <c r="B25" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="C25" s="11">
-        <v>1200</v>
-      </c>
-      <c r="D25" s="12">
-        <v>2.0000000000000002E-5</v>
-      </c>
-      <c r="E25" s="16">
-        <v>1E-4</v>
-      </c>
-      <c r="F25" s="11">
-        <v>0.45</v>
-      </c>
-      <c r="G25" s="6">
-        <v>4</v>
-      </c>
-      <c r="H25" s="13">
-        <v>6</v>
-      </c>
-      <c r="I25" s="14">
-        <v>0.3</v>
-      </c>
-      <c r="J25" s="11">
-        <v>1450</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10" ht="30.45" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A26" s="10">
-        <v>25</v>
-      </c>
-      <c r="B26" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="C26" s="11">
-        <v>1000</v>
-      </c>
-      <c r="D26" s="12">
-        <v>3.0000000000000001E-5</v>
-      </c>
-      <c r="E26" s="16">
-        <v>5.0000000000000001E-4</v>
-      </c>
-      <c r="F26" s="11">
-        <v>0.35</v>
-      </c>
-      <c r="G26" s="6">
-        <v>6</v>
-      </c>
-      <c r="H26" s="13">
-        <v>10</v>
-      </c>
-      <c r="I26" s="14">
-        <v>0.1</v>
-      </c>
-      <c r="J26" s="11">
-        <v>1150</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10" ht="30.45" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A27" s="10">
-        <v>26</v>
-      </c>
-      <c r="B27" s="11" t="s">
-        <v>36</v>
-      </c>
-      <c r="C27" s="11">
-        <v>600</v>
-      </c>
-      <c r="D27" s="12">
-        <v>4.0000000000000003E-5</v>
-      </c>
-      <c r="E27" s="16">
-        <v>2.9999999999999997E-4</v>
-      </c>
-      <c r="F27" s="11">
-        <v>0.35</v>
-      </c>
-      <c r="G27" s="6">
-        <v>5</v>
-      </c>
-      <c r="H27" s="13">
-        <v>8</v>
-      </c>
-      <c r="I27" s="14">
-        <v>0.08</v>
-      </c>
-      <c r="J27" s="11">
-        <v>1200</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10" ht="30.45" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A28" s="10">
-        <v>27</v>
-      </c>
-      <c r="B28" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="C28" s="11">
-        <v>2900</v>
-      </c>
-      <c r="D28" s="12">
-        <v>1.0000000000000001E-5</v>
-      </c>
-      <c r="E28" s="16">
-        <v>5</v>
-      </c>
-      <c r="F28" s="11">
-        <v>0.25</v>
-      </c>
-      <c r="G28" s="6">
-        <v>26</v>
-      </c>
-      <c r="H28" s="13">
-        <v>40</v>
-      </c>
-      <c r="I28" s="14">
-        <v>0.6</v>
-      </c>
-      <c r="J28" s="11">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10" ht="45.45" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A29" s="10">
-        <v>28</v>
-      </c>
-      <c r="B29" s="11" t="s">
+      <c r="I30" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="J30" s="11" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" ht="30.45" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A31" s="5">
+        <v>30</v>
+      </c>
+      <c r="B31" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="C29" s="11">
-        <v>400</v>
-      </c>
-      <c r="D29" s="12">
-        <v>1.5E-5</v>
-      </c>
-      <c r="E29" s="16">
-        <v>2.5000000000000001E-3</v>
-      </c>
-      <c r="F29" s="11">
-        <v>0.25</v>
-      </c>
-      <c r="G29" s="6">
-        <v>8</v>
-      </c>
-      <c r="H29" s="13">
-        <v>12</v>
-      </c>
-      <c r="I29" s="14">
-        <v>7.0000000000000007E-2</v>
-      </c>
-      <c r="J29" s="11">
-        <v>900</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10" ht="45.45" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A30" s="10">
-        <v>29</v>
-      </c>
-      <c r="B30" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="C30" s="11">
-        <v>2200</v>
-      </c>
-      <c r="D30" s="12">
-        <v>1.0000000000000001E-5</v>
-      </c>
-      <c r="E30" s="16">
-        <v>15</v>
-      </c>
-      <c r="F30" s="11">
-        <v>0.2</v>
-      </c>
-      <c r="G30" s="6">
-        <v>100</v>
-      </c>
-      <c r="H30" s="13">
-        <v>150</v>
-      </c>
-      <c r="I30" s="14">
-        <v>3</v>
-      </c>
-      <c r="J30" s="11">
-        <v>850</v>
-      </c>
-    </row>
-    <row r="31" spans="1:10" ht="30.45" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A31" s="10">
-        <v>30</v>
-      </c>
-      <c r="B31" s="11" t="s">
-        <v>40</v>
-      </c>
-      <c r="C31" s="11">
+      <c r="C31" s="6">
         <v>700</v>
       </c>
-      <c r="D31" s="12">
-        <v>4.0000000000000003E-5</v>
-      </c>
-      <c r="E31" s="16">
-        <v>2.0000000000000001E-4</v>
-      </c>
-      <c r="F31" s="11">
-        <v>0.35</v>
-      </c>
-      <c r="G31" s="6">
-        <v>4</v>
-      </c>
-      <c r="H31" s="13">
-        <v>6</v>
-      </c>
-      <c r="I31" s="14">
-        <v>7.0000000000000007E-2</v>
-      </c>
-      <c r="J31" s="11">
-        <v>1200</v>
+      <c r="D31" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="E31" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="F31" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="G31" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="H31" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="I31" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="J31" s="11" t="s">
+        <v>73</v>
       </c>
     </row>
   </sheetData>

--- a/mainWidget/mainWidget/src/database/外防热材料.xlsx
+++ b/mainWidget/mainWidget/src/database/外防热材料.xlsx
@@ -1,21 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="6" rupBuild="9303"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VSProject\git\GFApp\mainWidget\mainWidget\src\database\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA2F00C8-BE03-4719-B230-F895D7D5AE9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13320" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13320"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="145621"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -25,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="243" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="135">
   <si>
     <r>
       <rPr>
@@ -668,6 +662,342 @@
     </r>
   </si>
   <si>
+    <t>2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>13</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>20</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1500</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.35</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>40</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>60</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1300</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>6</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.0001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.0002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.25</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>100</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>8</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>26</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>12</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>150</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.07</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.6</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>900</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>850</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1200</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.45</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>66</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.08</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1250</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1400</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1450</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1150</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.22</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>140</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>166</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>210</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>250</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>800</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>750</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.17</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>133</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>90</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>200</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1100</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.16</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>300</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>350</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>233</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.14</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>950</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>53</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>80</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.06</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.05</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1050</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.03</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1350</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.00002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.000015</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.00001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.000005</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.000003</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.00005</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.00004</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.000002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.0000015</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.00003</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.00006</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2000000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4000000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>6000000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>15000000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>25000000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <r>
       <rPr>
         <b/>
@@ -687,375 +1017,59 @@
         <rFont val="Times New Roman"/>
         <family val="1"/>
       </rPr>
-      <t>[GPa]</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>13</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>20</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1500</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.35</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>4</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>40</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>60</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1300</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>6</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>15</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.0001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.0002</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.002</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.003</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>30</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.0025</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.25</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>100</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>8</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>26</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>12</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>150</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.07</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.6</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1000</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>900</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>850</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1200</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.0003</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.0005</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.45</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>66</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.08</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.4</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1250</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1400</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1450</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1150</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>38</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>35</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.22</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>140</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>166</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>210</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>250</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>800</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>750</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.17</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>133</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>90</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>200</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1100</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>29</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.16</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>300</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1.2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1.5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>350</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>233</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.14</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>950</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>53</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>80</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.06</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.05</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1050</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.03</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1350</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.00002</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.000015</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.00001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.000005</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.000003</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.00005</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.00004</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.000002</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.0000015</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.00003</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.00006</t>
+      <t>[MPa]</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>30000000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>35000000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10000000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>24000000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>29000000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>38000000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>500</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>5000000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2500</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -1494,14 +1508,14 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:J31"/>
   <sheetFormatPr defaultRowHeight="14.15" x14ac:dyDescent="0.35"/>
   <cols>
@@ -1524,7 +1538,7 @@
         <v>3</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>39</v>
+        <v>123</v>
       </c>
       <c r="F1" s="8" t="s">
         <v>4</v>
@@ -1553,25 +1567,25 @@
         <v>1200</v>
       </c>
       <c r="D2" s="10" t="s">
-        <v>119</v>
+        <v>107</v>
       </c>
       <c r="E2" s="10" t="s">
+        <v>118</v>
+      </c>
+      <c r="F2" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="G2" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="F2" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="G2" s="10" t="s">
+      <c r="H2" s="10" t="s">
         <v>41</v>
-      </c>
-      <c r="H2" s="10" t="s">
-        <v>42</v>
       </c>
       <c r="I2" s="10">
         <v>0.3</v>
       </c>
       <c r="J2" s="10" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="45.45" thickBot="1" x14ac:dyDescent="0.4">
@@ -1585,25 +1599,25 @@
         <v>1600</v>
       </c>
       <c r="D3" s="11" t="s">
-        <v>120</v>
+        <v>108</v>
       </c>
       <c r="E3" s="11" t="s">
+        <v>119</v>
+      </c>
+      <c r="F3" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="F3" s="11" t="s">
+      <c r="G3" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="G3" s="10" t="s">
+      <c r="H3" s="11" t="s">
         <v>47</v>
-      </c>
-      <c r="H3" s="11" t="s">
-        <v>48</v>
       </c>
       <c r="I3" s="11">
         <v>0.4</v>
       </c>
       <c r="J3" s="11" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="30.45" thickBot="1" x14ac:dyDescent="0.4">
@@ -1617,25 +1631,25 @@
         <v>1700</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>50</v>
+        <v>120</v>
       </c>
       <c r="F4" s="11" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="G4" s="10" t="s">
-        <v>111</v>
+        <v>99</v>
       </c>
       <c r="H4" s="11" t="s">
-        <v>112</v>
+        <v>100</v>
       </c>
       <c r="I4" s="11" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="J4" s="11" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="16.3" thickBot="1" x14ac:dyDescent="0.4">
@@ -1649,25 +1663,25 @@
         <v>1800</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>122</v>
+        <v>110</v>
       </c>
       <c r="E5" s="11" t="s">
-        <v>51</v>
+        <v>121</v>
       </c>
       <c r="F5" s="11" t="s">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="G5" s="10" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="H5" s="11" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="I5" s="11" t="s">
-        <v>106</v>
+        <v>94</v>
       </c>
       <c r="J5" s="11" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="46.3" thickBot="1" x14ac:dyDescent="0.4">
@@ -1681,25 +1695,25 @@
         <v>2000</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>123</v>
-      </c>
-      <c r="E6" s="11">
-        <v>25</v>
+        <v>111</v>
+      </c>
+      <c r="E6" s="11" t="s">
+        <v>122</v>
       </c>
       <c r="F6" s="11" t="s">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="G6" s="10" t="s">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="H6" s="11" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="I6" s="11" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="J6" s="11" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
     </row>
     <row r="7" spans="1:10" ht="30.45" thickBot="1" x14ac:dyDescent="0.4">
@@ -1713,25 +1727,25 @@
         <v>20</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>124</v>
+        <v>112</v>
       </c>
       <c r="E7" s="11" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="F7" s="11" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G7" s="10" t="s">
-        <v>113</v>
+        <v>101</v>
       </c>
       <c r="H7" s="11" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
       <c r="I7" s="11" t="s">
-        <v>115</v>
+        <v>103</v>
       </c>
       <c r="J7" s="11" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="30.45" thickBot="1" x14ac:dyDescent="0.4">
@@ -1745,25 +1759,25 @@
         <v>30</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>129</v>
+        <v>117</v>
       </c>
       <c r="E8" s="11" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G8" s="10" t="s">
-        <v>113</v>
+        <v>101</v>
       </c>
       <c r="H8" s="11" t="s">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="I8" s="11" t="s">
-        <v>114</v>
+        <v>102</v>
       </c>
       <c r="J8" s="11" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
     </row>
     <row r="9" spans="1:10" ht="30.45" thickBot="1" x14ac:dyDescent="0.4">
@@ -1777,25 +1791,25 @@
         <v>100</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>125</v>
+        <v>113</v>
       </c>
       <c r="E9" s="11" t="s">
-        <v>53</v>
+        <v>87</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G9" s="10" t="s">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="H9" s="11" t="s">
+        <v>94</v>
+      </c>
+      <c r="I9" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="J9" s="11" t="s">
         <v>106</v>
-      </c>
-      <c r="I9" s="11" t="s">
-        <v>115</v>
-      </c>
-      <c r="J9" s="11" t="s">
-        <v>118</v>
       </c>
     </row>
     <row r="10" spans="1:10" ht="30.45" thickBot="1" x14ac:dyDescent="0.4">
@@ -1809,25 +1823,25 @@
         <v>300</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
       <c r="E10" s="11" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G10" s="10" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="H10" s="11" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="I10" s="11" t="s">
-        <v>117</v>
+        <v>105</v>
       </c>
       <c r="J10" s="11" t="s">
-        <v>101</v>
+        <v>90</v>
       </c>
     </row>
     <row r="11" spans="1:10" ht="30.45" thickBot="1" x14ac:dyDescent="0.4">
@@ -1841,25 +1855,25 @@
         <v>200</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>119</v>
+        <v>107</v>
       </c>
       <c r="E11" s="11" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="F11" s="11" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G11" s="10" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="H11" s="11" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="I11" s="11" t="s">
-        <v>79</v>
+        <v>70</v>
       </c>
       <c r="J11" s="11" t="s">
-        <v>116</v>
+        <v>104</v>
       </c>
     </row>
     <row r="12" spans="1:10" ht="45.45" thickBot="1" x14ac:dyDescent="0.4">
@@ -1873,25 +1887,25 @@
         <v>300</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>120</v>
+        <v>108</v>
       </c>
       <c r="E12" s="11" t="s">
-        <v>55</v>
+        <v>124</v>
       </c>
       <c r="F12" s="11" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G12" s="10" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="H12" s="11" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="I12" s="11" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="J12" s="11" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
     </row>
     <row r="13" spans="1:10" ht="45.45" thickBot="1" x14ac:dyDescent="0.4">
@@ -1905,25 +1919,25 @@
         <v>400</v>
       </c>
       <c r="D13" s="11" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
       <c r="E13" s="11" t="s">
-        <v>56</v>
+        <v>125</v>
       </c>
       <c r="F13" s="11" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G13" s="10" t="s">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="H13" s="11" t="s">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="I13" s="11" t="s">
-        <v>114</v>
+        <v>102</v>
       </c>
       <c r="J13" s="11" t="s">
-        <v>110</v>
+        <v>98</v>
       </c>
     </row>
     <row r="14" spans="1:10" ht="60.45" thickBot="1" x14ac:dyDescent="0.4">
@@ -1937,25 +1951,25 @@
         <v>2500</v>
       </c>
       <c r="D14" s="11" t="s">
+        <v>114</v>
+      </c>
+      <c r="E14" s="11" t="s">
         <v>126</v>
       </c>
-      <c r="E14" s="11" t="s">
-        <v>57</v>
-      </c>
       <c r="F14" s="11" t="s">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="G14" s="10" t="s">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="H14" s="11" t="s">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="I14" s="11" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="J14" s="11" t="s">
-        <v>93</v>
+        <v>82</v>
       </c>
     </row>
     <row r="15" spans="1:10" ht="60.45" thickBot="1" x14ac:dyDescent="0.4">
@@ -1969,25 +1983,25 @@
         <v>2800</v>
       </c>
       <c r="D15" s="11" t="s">
+        <v>115</v>
+      </c>
+      <c r="E15" s="11" t="s">
         <v>127</v>
       </c>
-      <c r="E15" s="11" t="s">
-        <v>87</v>
-      </c>
       <c r="F15" s="11" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="G15" s="10" t="s">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="H15" s="11" t="s">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="I15" s="11" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="J15" s="11" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
     </row>
     <row r="16" spans="1:10" ht="45.45" thickBot="1" x14ac:dyDescent="0.4">
@@ -2001,25 +2015,25 @@
         <v>1800</v>
       </c>
       <c r="D16" s="11" t="s">
-        <v>119</v>
+        <v>107</v>
       </c>
       <c r="E16" s="11" t="s">
-        <v>50</v>
+        <v>120</v>
       </c>
       <c r="F16" s="11" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G16" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="H16" s="11" t="s">
+        <v>86</v>
+      </c>
+      <c r="I16" s="11" t="s">
+        <v>89</v>
+      </c>
+      <c r="J16" s="11" t="s">
         <v>48</v>
-      </c>
-      <c r="H16" s="11" t="s">
-        <v>97</v>
-      </c>
-      <c r="I16" s="11" t="s">
-        <v>100</v>
-      </c>
-      <c r="J16" s="11" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="17" spans="1:10" ht="45.45" thickBot="1" x14ac:dyDescent="0.4">
@@ -2033,25 +2047,25 @@
         <v>1400</v>
       </c>
       <c r="D17" s="11" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
       <c r="E17" s="11" t="s">
-        <v>78</v>
+        <v>128</v>
       </c>
       <c r="F17" s="11" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="G17" s="10" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="H17" s="11" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="I17" s="11" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="J17" s="11" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
     </row>
     <row r="18" spans="1:10" ht="61.3" thickBot="1" x14ac:dyDescent="0.4">
@@ -2065,25 +2079,25 @@
         <v>1750</v>
       </c>
       <c r="D18" s="11" t="s">
-        <v>122</v>
-      </c>
-      <c r="E18" s="11">
-        <v>24</v>
+        <v>110</v>
+      </c>
+      <c r="E18" s="11" t="s">
+        <v>129</v>
       </c>
       <c r="F18" s="11" t="s">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="G18" s="10" t="s">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="H18" s="11" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="I18" s="11" t="s">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="J18" s="11" t="s">
-        <v>101</v>
+        <v>90</v>
       </c>
     </row>
     <row r="19" spans="1:10" ht="61.3" thickBot="1" x14ac:dyDescent="0.4">
@@ -2097,25 +2111,25 @@
         <v>1900</v>
       </c>
       <c r="D19" s="11" t="s">
-        <v>123</v>
+        <v>111</v>
       </c>
       <c r="E19" s="11" t="s">
-        <v>102</v>
+        <v>130</v>
       </c>
       <c r="F19" s="11" t="s">
-        <v>103</v>
+        <v>91</v>
       </c>
       <c r="G19" s="10" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="H19" s="11" t="s">
-        <v>104</v>
+        <v>92</v>
       </c>
       <c r="I19" s="11" t="s">
-        <v>105</v>
+        <v>93</v>
       </c>
       <c r="J19" s="11" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
     </row>
     <row r="20" spans="1:10" ht="61.3" thickBot="1" x14ac:dyDescent="0.4">
@@ -2129,25 +2143,25 @@
         <v>2000</v>
       </c>
       <c r="D20" s="11" t="s">
-        <v>126</v>
+        <v>114</v>
       </c>
       <c r="E20" s="11" t="s">
-        <v>86</v>
+        <v>131</v>
       </c>
       <c r="F20" s="11" t="s">
-        <v>109</v>
+        <v>97</v>
       </c>
       <c r="G20" s="10" t="s">
-        <v>108</v>
+        <v>96</v>
       </c>
       <c r="H20" s="11" t="s">
-        <v>107</v>
+        <v>95</v>
       </c>
       <c r="I20" s="11" t="s">
-        <v>106</v>
+        <v>94</v>
       </c>
       <c r="J20" s="11" t="s">
-        <v>110</v>
+        <v>98</v>
       </c>
     </row>
     <row r="21" spans="1:10" ht="45.45" thickBot="1" x14ac:dyDescent="0.4">
@@ -2161,25 +2175,25 @@
         <v>2200</v>
       </c>
       <c r="D21" s="11" t="s">
-        <v>123</v>
+        <v>111</v>
       </c>
       <c r="E21" s="11" t="s">
-        <v>57</v>
+        <v>126</v>
       </c>
       <c r="F21" s="11">
         <v>0.15</v>
       </c>
       <c r="G21" s="10" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="H21" s="11" t="s">
-        <v>104</v>
+        <v>92</v>
       </c>
       <c r="I21" s="11">
         <v>1.3</v>
       </c>
       <c r="J21" s="11" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
     </row>
     <row r="22" spans="1:10" ht="45.45" thickBot="1" x14ac:dyDescent="0.4">
@@ -2193,25 +2207,25 @@
         <v>1900</v>
       </c>
       <c r="D22" s="11" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
       <c r="E22" s="11" t="s">
-        <v>50</v>
+        <v>120</v>
       </c>
       <c r="F22" s="11" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="G22" s="10" t="s">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="H22" s="11" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="I22" s="11" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="J22" s="11" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
     </row>
     <row r="23" spans="1:10" ht="30.45" thickBot="1" x14ac:dyDescent="0.4">
@@ -2225,25 +2239,25 @@
         <v>1300</v>
       </c>
       <c r="D23" s="11" t="s">
-        <v>119</v>
+        <v>107</v>
       </c>
       <c r="E23" s="11" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F23" s="11" t="s">
-        <v>76</v>
+        <v>67</v>
       </c>
       <c r="G23" s="10" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="H23" s="11">
         <v>5</v>
       </c>
       <c r="I23" s="11" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="J23" s="11" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
     </row>
     <row r="24" spans="1:10" ht="30.45" thickBot="1" x14ac:dyDescent="0.4">
@@ -2257,25 +2271,25 @@
         <v>1500</v>
       </c>
       <c r="D24" s="11" t="s">
-        <v>120</v>
+        <v>108</v>
       </c>
       <c r="E24" s="11" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="F24" s="11" t="s">
-        <v>76</v>
+        <v>67</v>
       </c>
       <c r="G24" s="10" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="H24" s="11" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="I24" s="11" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="J24" s="11" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="25" spans="1:10" ht="45.45" thickBot="1" x14ac:dyDescent="0.4">
@@ -2289,25 +2303,25 @@
         <v>1200</v>
       </c>
       <c r="D25" s="11" t="s">
-        <v>119</v>
+        <v>107</v>
       </c>
       <c r="E25" s="11" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="F25" s="11" t="s">
-        <v>76</v>
+        <v>67</v>
       </c>
       <c r="G25" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="H25" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="I25" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="H25" s="11" t="s">
-        <v>50</v>
-      </c>
-      <c r="I25" s="11" t="s">
-        <v>46</v>
-      </c>
       <c r="J25" s="11" t="s">
-        <v>84</v>
+        <v>75</v>
       </c>
     </row>
     <row r="26" spans="1:10" ht="30.45" thickBot="1" x14ac:dyDescent="0.4">
@@ -2321,25 +2335,25 @@
         <v>1000</v>
       </c>
       <c r="D26" s="11" t="s">
-        <v>128</v>
+        <v>116</v>
       </c>
       <c r="E26" s="11" t="s">
-        <v>75</v>
+        <v>132</v>
       </c>
       <c r="F26" s="11" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G26" s="10" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="H26" s="11" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="I26" s="11" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="J26" s="11" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
     </row>
     <row r="27" spans="1:10" ht="30.45" thickBot="1" x14ac:dyDescent="0.4">
@@ -2353,25 +2367,25 @@
         <v>600</v>
       </c>
       <c r="D27" s="11" t="s">
-        <v>125</v>
+        <v>113</v>
       </c>
       <c r="E27" s="11" t="s">
-        <v>74</v>
+        <v>92</v>
       </c>
       <c r="F27" s="11" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G27" s="10" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="H27" s="11" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="I27" s="11" t="s">
-        <v>79</v>
+        <v>70</v>
       </c>
       <c r="J27" s="11" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
     </row>
     <row r="28" spans="1:10" ht="30.45" thickBot="1" x14ac:dyDescent="0.4">
@@ -2385,25 +2399,25 @@
         <v>2900</v>
       </c>
       <c r="D28" s="11" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
       <c r="E28" s="11" t="s">
-        <v>59</v>
+        <v>133</v>
       </c>
       <c r="F28" s="11" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="G28" s="10" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="H28" s="11" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="I28" s="11" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="J28" s="11" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
     </row>
     <row r="29" spans="1:10" ht="45.45" thickBot="1" x14ac:dyDescent="0.4">
@@ -2417,25 +2431,25 @@
         <v>400</v>
       </c>
       <c r="D29" s="11" t="s">
-        <v>120</v>
+        <v>108</v>
       </c>
       <c r="E29" s="11" t="s">
+        <v>134</v>
+      </c>
+      <c r="F29" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="G29" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="H29" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="F29" s="11" t="s">
+      <c r="I29" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="G29" s="10" t="s">
-        <v>63</v>
-      </c>
-      <c r="H29" s="11" t="s">
-        <v>65</v>
-      </c>
-      <c r="I29" s="11" t="s">
-        <v>67</v>
-      </c>
       <c r="J29" s="11" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
     </row>
     <row r="30" spans="1:10" ht="45.45" thickBot="1" x14ac:dyDescent="0.4">
@@ -2449,25 +2463,25 @@
         <v>2200</v>
       </c>
       <c r="D30" s="11" t="s">
+        <v>109</v>
+      </c>
+      <c r="E30" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="E30" s="11" t="s">
-        <v>51</v>
-      </c>
       <c r="F30" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="G30" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="H30" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="I30" s="11" t="s">
         <v>61</v>
       </c>
-      <c r="G30" s="10" t="s">
-        <v>62</v>
-      </c>
-      <c r="H30" s="11" t="s">
-        <v>66</v>
-      </c>
-      <c r="I30" s="11" t="s">
-        <v>68</v>
-      </c>
       <c r="J30" s="11" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
     </row>
     <row r="31" spans="1:10" ht="30.45" thickBot="1" x14ac:dyDescent="0.4">
@@ -2481,25 +2495,25 @@
         <v>700</v>
       </c>
       <c r="D31" s="11" t="s">
-        <v>125</v>
+        <v>113</v>
       </c>
       <c r="E31" s="11" t="s">
-        <v>53</v>
+        <v>87</v>
       </c>
       <c r="F31" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="G31" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="G31" s="10" t="s">
-        <v>45</v>
-      </c>
       <c r="H31" s="11" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="I31" s="11" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="J31" s="11" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
     </row>
   </sheetData>
